--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_valparaiso.xlsx
@@ -96,12 +96,12 @@
     <t xml:space="preserve">Juan Fernández</t>
   </si>
   <si>
+    <t xml:space="preserve">Hijuelas</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Esteban</t>
   </si>
   <si>
-    <t xml:space="preserve">Hijuelas</t>
-  </si>
-  <si>
     <t xml:space="preserve">Catemu</t>
   </si>
   <si>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:40</t>
+    <t xml:space="preserve">2026-09-09 22:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -937,7 +937,7 @@
         <v>26</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>5304</v>
+        <v>5503</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2019</v>
@@ -954,7 +954,7 @@
         <v>27</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>5503</v>
+        <v>5304</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2019</v>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:26</t>
+    <t xml:space="preserve">2026-09-12 19:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_valparaiso.xlsx
@@ -96,12 +96,12 @@
     <t xml:space="preserve">Juan Fernández</t>
   </si>
   <si>
+    <t xml:space="preserve">San Esteban</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hijuelas</t>
   </si>
   <si>
-    <t xml:space="preserve">San Esteban</t>
-  </si>
-  <si>
     <t xml:space="preserve">Catemu</t>
   </si>
   <si>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:43</t>
+    <t xml:space="preserve">2026-09-24 00:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -937,7 +937,7 @@
         <v>26</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>5503</v>
+        <v>5304</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2019</v>
@@ -954,7 +954,7 @@
         <v>27</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>5304</v>
+        <v>5503</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2019</v>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:20</t>
+    <t xml:space="preserve">2026-09-27 22:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:09</t>
+    <t xml:space="preserve">2026-10-01 20:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:50</t>
+    <t xml:space="preserve">2026-10-02 13:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:16</t>
+    <t xml:space="preserve">2026-10-04 08:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:03</t>
+    <t xml:space="preserve">2026-10-05 07:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
